--- a/parameters.xlsx
+++ b/parameters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IndexY\Desktop\paralle_\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE32D3D0-0968-4026-9037-F07A3BE21B22}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{919A26C7-E2C1-489A-8D1E-E550BA1EEF1F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="480" yWindow="60" windowWidth="18192" windowHeight="8508" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1230,7 +1230,7 @@
         <v>15</v>
       </c>
       <c r="B10" s="16">
-        <v>150</v>
+        <v>7.5</v>
       </c>
       <c r="C10" s="16">
         <v>150</v>
@@ -1837,7 +1837,7 @@
         <v>26</v>
       </c>
       <c r="B22" s="16">
-        <v>600</v>
+        <v>888.40221699999995</v>
       </c>
       <c r="C22" s="16">
         <v>600</v>
@@ -1884,7 +1884,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="16">
-        <v>600</v>
+        <v>890.64050899999995</v>
       </c>
       <c r="C23" s="16">
         <v>600</v>
@@ -1925,7 +1925,7 @@
         <v>28</v>
       </c>
       <c r="B24" s="16">
-        <v>600</v>
+        <v>890.64050899999995</v>
       </c>
       <c r="C24" s="16">
         <v>600</v>
@@ -1966,7 +1966,7 @@
         <v>29</v>
       </c>
       <c r="B25" s="16">
-        <v>600</v>
+        <v>795.90020100000004</v>
       </c>
       <c r="C25" s="16">
         <v>600</v>
@@ -2007,7 +2007,7 @@
         <v>30</v>
       </c>
       <c r="B26" s="16">
-        <v>600</v>
+        <v>795.90020100000004</v>
       </c>
       <c r="C26" s="16">
         <v>600</v>
